--- a/TestData/T2022_GiftLog_GiftRequestProcess_VerifyTheYearlyGiftAllowanceExceedLimitForTheNewGiftTotalNextYear.xlsx
+++ b/TestData/T2022_GiftLog_GiftRequestProcess_VerifyTheYearlyGiftAllowanceExceedLimitForTheNewGiftTotalNextYear.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20390"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BD8A67-0D4D-430F-AC01-2D9D1F60CAAD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C22920A-BB3E-44AC-B939-932A27D97B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="6804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GiftLog" sheetId="4" r:id="rId1"/>
-    <sheet name="Users" sheetId="5" r:id="rId2"/>
+    <sheet name="Users" sheetId="5" r:id="rId1"/>
+    <sheet name="AppName" sheetId="6" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="7" r:id="rId3"/>
+    <sheet name="GiftLog" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Client Gift Pre-approval</t>
   </si>
@@ -125,6 +127,15 @@
   </si>
   <si>
     <t>Red</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Gift Requests</t>
   </si>
 </sst>
 </file>
@@ -454,6 +465,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A84B2636-CA03-42D3-96C8-11C13FAF74A4}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{585BEC6D-C9ED-497D-B7BA-C939197A4CC7}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -571,35 +653,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>